--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JagalchiHang\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F46BC65-7869-4BBC-994C-5EBB2FAC52DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810604BB-5B12-43A9-BFFF-B7338433CAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3165" yWindow="1635" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t>아이템 이름</t>
   </si>
@@ -46,9 +46,6 @@
     <t>아이템 사용 효과 설명</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -56,12 +53,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>IconPath</t>
   </si>
   <si>
     <t>IsStackable</t>
@@ -141,13 +132,49 @@
   <si>
     <t>item1</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconPath</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이디</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_02</t>
+  </si>
+  <si>
+    <t>Item_03</t>
+  </si>
+  <si>
+    <t>Item_04</t>
+  </si>
+  <si>
+    <t>Item_05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -166,6 +193,20 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -189,9 +230,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -410,53 +453,56 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>10</v>
@@ -465,151 +511,172 @@
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="1" t="b">
+    <row r="5" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="D4" s="1">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="b">
+      <c r="E6" s="1">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="b">
+      <c r="G6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E7" s="1">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="b">
+      <c r="F7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="b">
+      <c r="E8" s="1">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="D7" s="1">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -14,162 +14,180 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sprite/Water_Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
   <x:si>
     <x:t>MaxDropCount</x:t>
   </x:si>
   <x:si>
-    <x:t>MinDropCount</x:t>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sprite/WoodStick_Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sprite/WoodPiece_Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sprite/IronPiece_Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sprite/Can_Icon</x:t>
   </x:si>
   <x:si>
     <x:t>아이템 사용 효과</x:t>
   </x:si>
   <x:si>
+    <x:t>1번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3번아이템 사용!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1번아이템 사용!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
     <x:t>IsStackable</x:t>
   </x:si>
   <x:si>
+    <x:t>5번아이템 사용!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
     <x:t>MaxCount</x:t>
   </x:si>
   <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3번 아이템 효과다!</x:t>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2번아이템 사용!</x:t>
   </x:si>
   <x:si>
     <x:t>4번아이템 사용</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
+    <x:t>Item_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>type3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>type2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Type1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>type5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>type4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
   </x:si>
   <x:si>
     <x:t>아이콘 경로</x:t>
   </x:si>
   <x:si>
-    <x:t>Type1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>item1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
+    <x:t>나무 조각</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -981,124 +999,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F1" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="K1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I3" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L3" t="s">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="I3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L3" t="s">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -1110,13 +1131,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J4">
         <x:v>1</x:v>
@@ -1130,13 +1151,16 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>10</x:v>
@@ -1145,13 +1169,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J5">
         <x:v>1</x:v>
@@ -1165,10 +1189,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1180,13 +1207,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J6">
         <x:v>1</x:v>
@@ -1200,13 +1227,16 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C7" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>10</x:v>
@@ -1215,13 +1245,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J7">
         <x:v>2</x:v>
@@ -1235,13 +1265,16 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C8" t="s">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="1">
         <x:v>10</x:v>
@@ -1250,13 +1283,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J8">
         <x:v>2</x:v>
@@ -1269,7 +1302,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -19,7 +19,100 @@
     <x:t>UseItemDescription</x:t>
   </x:si>
   <x:si>
-    <x:t>Sprite/Water_Icon</x:t>
+    <x:t>4번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1번아이템 사용!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3번아이템 사용!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2번 아이템 효과다!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4번아이템 사용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5번아이템 사용!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2번아이템 사용!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image_Icon/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image_Icon/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
   </x:si>
   <x:si>
     <x:t>MinDropCount</x:t>
@@ -31,163 +124,70 @@
     <x:t>MaxDropCount</x:t>
   </x:si>
   <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
     <x:t>아이템 사용 가능 여부</x:t>
   </x:si>
   <x:si>
+    <x:t>type3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>type4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Type1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>type2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>type5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image_Icon/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image_Icon/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image_Icon/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
     <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sprite/WoodStick_Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sprite/WoodPiece_Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sprite/IronPiece_Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sprite/Can_Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4번아이템 사용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Type1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -999,127 +999,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L1" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K3" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>4</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -1131,13 +1131,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J4">
         <x:v>1</x:v>
@@ -1151,13 +1151,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="C5" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -1169,13 +1169,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J5">
         <x:v>1</x:v>
@@ -1189,13 +1189,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>1</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1207,13 +1207,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="J6">
         <x:v>1</x:v>
@@ -1227,13 +1227,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
@@ -1245,13 +1245,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J7">
         <x:v>2</x:v>
@@ -1265,13 +1265,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>1</x:v>
@@ -1283,13 +1283,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="J8">
         <x:v>2</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -14,180 +14,216 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
   <x:si>
     <x:t>UseItemDescription</x:t>
   </x:si>
   <x:si>
-    <x:t>4번 아이템 효과다!</x:t>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
   </x:si>
   <x:si>
     <x:t>ItemName</x:t>
   </x:si>
   <x:si>
-    <x:t>아이템 등장 가중치</x:t>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
   </x:si>
   <x:si>
     <x:t>string[]</x:t>
   </x:si>
   <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
   </x:si>
   <x:si>
     <x:t>아이템 사용 효과</x:t>
   </x:si>
   <x:si>
-    <x:t>1번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2번 아이템 효과다!</x:t>
-  </x:si>
-  <x:si>
     <x:t>UseItemType</x:t>
   </x:si>
   <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
+    <x:t>IsStackable</x:t>
   </x:si>
   <x:si>
     <x:t>MaxCount</x:t>
   </x:si>
   <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4번아이템 사용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2번아이템 사용!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image_Icon/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image_Icon/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type4</x:t>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_02</x:t>
   </x:si>
   <x:si>
     <x:t>bool</x:t>
   </x:si>
   <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
     <x:t>나무 조각</x:t>
   </x:si>
   <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Type1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>type5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image_Icon/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image_Icon/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image_Icon/Image_WoodStick</x:t>
+    <x:t>전자 칩</x:t>
   </x:si>
   <x:si>
     <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Grain</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -987,11 +1023,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L8"/>
+  <x:dimension ref="A1:L22"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <x:col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="18" customWidth="1"/>
+    <x:col min="7" max="7" width="15.66796875" customWidth="1"/>
     <x:col min="8" max="8" width="17.42578125" customWidth="1"/>
     <x:col min="9" max="9" width="18.7109375" customWidth="1"/>
     <x:col min="10" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -999,154 +1037,145 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>5</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K3" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="1">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="1">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="F4" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H4" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I4" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
       <x:c r="J4">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K4">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L4">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
@@ -1154,151 +1183,443 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E5" s="1">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F5" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H5" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="I5" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
+      <x:c r="G5" s="1"/>
+      <x:c r="H5" s="1"/>
+      <x:c r="I5" s="1"/>
       <x:c r="J5">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K5">
         <x:v>2</x:v>
       </x:c>
       <x:c r="L5">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C6" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="1">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F6" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="I6" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="1"/>
+      <x:c r="H6" s="1"/>
+      <x:c r="I6" s="1"/>
       <x:c r="J6">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K6">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L6">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="1">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F7" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="1"/>
+      <x:c r="H7" s="1"/>
+      <x:c r="I7" s="1"/>
       <x:c r="J7">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K7">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K7">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="L7">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="1"/>
+      <x:c r="H8" s="1"/>
+      <x:c r="I8" s="1"/>
+      <x:c r="J8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L8">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:12" customHeight="1">
+      <x:c r="A9" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" s="1">
+      <x:c r="B9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L9">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:12" customHeight="1">
+      <x:c r="A10" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D10" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F10" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L10">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:12" customHeight="1">
+      <x:c r="A11" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D11" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K11">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L11">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:10" customHeight="1">
+      <x:c r="A12" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D12" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F12" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:10" customHeight="1">
+      <x:c r="A13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10" customHeight="1">
+      <x:c r="A14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D14" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10" customHeight="1">
+      <x:c r="A15" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B15" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D15" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F15" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10" customHeight="1">
+      <x:c r="A16" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B16" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D16" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F16" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10" customHeight="1">
+      <x:c r="A17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B17" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F17" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10" customHeight="1">
+      <x:c r="A18" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B18" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D18" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F18" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10" customHeight="1">
+      <x:c r="A19" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B19" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D19" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F19" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10" customHeight="1">
+      <x:c r="A20" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B20" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D20" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F20" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:12" customHeight="1">
+      <x:c r="A21" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B21" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D21" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H8" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="I8" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8">
+      <x:c r="F21" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H21">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I21" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L8">
+      <x:c r="J21">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K21">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L21">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:12" customHeight="1">
+      <x:c r="A22" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B22" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D22" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22">
         <x:v>10</x:v>
+      </x:c>
+      <x:c r="F22" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H22">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I22" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J22">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K22">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L22">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -16,214 +16,214 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <x:si>
+    <x:t>갈증을 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
     <x:t>감자</x:t>
   </x:si>
   <x:si>
-    <x:t>갈증을 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_04</x:t>
   </x:si>
   <x:si>
     <x:t>Hunger</x:t>
   </x:si>
   <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_03</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_05</x:t>
+  </x:si>
+  <x:si>
     <x:t>최대수량</x:t>
   </x:si>
   <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Grain</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
+    <x:t>Item_10</x:t>
   </x:si>
   <x:si>
     <x:t>Thirsty</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
+    <x:t>Crop_Wheat</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1037,121 +1037,121 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>25</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>29</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>28</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K3" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>9</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>49</x:v>
@@ -1180,10 +1180,10 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -1209,10 +1209,10 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1238,10 +1238,10 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
@@ -1267,10 +1267,10 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>0</x:v>
@@ -1299,7 +1299,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D9" t="b">
         <x:v>0</x:v>
@@ -1322,10 +1322,10 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D10" t="b">
         <x:v>0</x:v>
@@ -1348,10 +1348,10 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" t="b">
         <x:v>1</x:v>
@@ -1374,10 +1374,10 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" t="b">
         <x:v>1</x:v>
@@ -1394,10 +1394,10 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" t="s">
-        <x:v>54</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D13" t="b">
         <x:v>1</x:v>
@@ -1414,10 +1414,10 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" t="s">
-        <x:v>63</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D14" t="b">
         <x:v>1</x:v>
@@ -1434,10 +1434,10 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" t="s">
-        <x:v>61</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D15" t="b">
         <x:v>1</x:v>
@@ -1454,10 +1454,10 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D16" t="b">
         <x:v>1</x:v>
@@ -1474,10 +1474,10 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D17" t="b">
         <x:v>1</x:v>
@@ -1494,10 +1494,10 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D18" t="b">
         <x:v>1</x:v>
@@ -1514,10 +1514,10 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>5</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D19" t="b">
         <x:v>1</x:v>
@@ -1534,10 +1534,10 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>4</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D20" t="b">
         <x:v>1</x:v>
@@ -1554,10 +1554,10 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D21" t="b">
         <x:v>1</x:v>
@@ -1569,13 +1569,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>3</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H21">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J21">
         <x:v>2</x:v>
@@ -1589,10 +1589,10 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" t="s">
-        <x:v>24</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D22" t="b">
         <x:v>1</x:v>
@@ -1604,13 +1604,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H22">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J22">
         <x:v>2</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -14,216 +14,225 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
   <x:si>
     <x:t>갈증을 50 채워준다</x:t>
   </x:si>
   <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
     <x:t>아이템 사용 종류</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
     <x:t>감자</x:t>
   </x:si>
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
     <x:t>물</x:t>
   </x:si>
   <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
     <x:t>막대기</x:t>
   </x:si>
   <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
+    <x:t>Item_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_10</x:t>
   </x:si>
   <x:si>
     <x:t>UseItemParameterList</x:t>
   </x:si>
   <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
+    <x:t>Images/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Image_IronPiece</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1040,113 +1049,113 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="K1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L1" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="L1" t="s">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="C3" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H3" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I3" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="J3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I3" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J3" t="s">
+      <x:c r="K3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K3" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="L3" t="s">
-        <x:v>42</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
@@ -1154,7 +1163,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C4" t="s">
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -1180,10 +1192,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C5" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -1209,10 +1224,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="3" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C6" t="s">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1238,10 +1256,10 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
@@ -1267,10 +1285,10 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>0</x:v>
@@ -1296,7 +1314,7 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" t="s">
         <x:v>37</x:v>
@@ -1322,10 +1340,10 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D10" t="b">
         <x:v>0</x:v>
@@ -1348,10 +1366,10 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D11" t="b">
         <x:v>1</x:v>
@@ -1374,10 +1392,10 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D12" t="b">
         <x:v>1</x:v>
@@ -1397,7 +1415,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D13" t="b">
         <x:v>1</x:v>
@@ -1414,7 +1432,7 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" t="s">
         <x:v>32</x:v>
@@ -1434,10 +1452,10 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D15" t="b">
         <x:v>1</x:v>
@@ -1457,7 +1475,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D16" t="b">
         <x:v>1</x:v>
@@ -1474,10 +1492,10 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" t="b">
         <x:v>1</x:v>
@@ -1494,10 +1512,10 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" t="s">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>24</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D18" t="b">
         <x:v>1</x:v>
@@ -1514,10 +1532,10 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D19" t="b">
         <x:v>1</x:v>
@@ -1534,10 +1552,10 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" t="s">
-        <x:v>69</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>28</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D20" t="b">
         <x:v>1</x:v>
@@ -1554,10 +1572,10 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D21" t="b">
         <x:v>1</x:v>
@@ -1569,13 +1587,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H21">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>1</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J21">
         <x:v>2</x:v>
@@ -1589,10 +1607,10 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D22" t="b">
         <x:v>1</x:v>
@@ -1610,7 +1628,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>0</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="J22">
         <x:v>2</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -14,225 +14,246 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
+  <x:si>
+    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
   <x:si>
     <x:t>MaxDropCount</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
     <x:t>UseItemDescription</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_04</x:t>
   </x:si>
   <x:si>
     <x:t>Item_07</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
     <x:t>철 조각</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_11</x:t>
-  </x:si>
-  <x:si>
     <x:t>식물성 기름</x:t>
   </x:si>
   <x:si>
     <x:t>나무 조각</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
     <x:t>Thirsty</x:t>
   </x:si>
   <x:si>
     <x:t>Item_10</x:t>
   </x:si>
   <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Image_IronPiece</x:t>
+    <x:t>Images/Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -361,7 +382,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -373,6 +394,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1035,6 +1059,7 @@
   <x:dimension ref="A1:L22"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
+    <x:col min="3" max="3" width="37.33203125" customWidth="1"/>
     <x:col min="4" max="4" width="19.5703125" customWidth="1"/>
     <x:col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="18" customWidth="1"/>
@@ -1046,31 +1071,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J1" t="s">
         <x:v>10</x:v>
@@ -1079,94 +1104,94 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K3" t="s">
-        <x:v>3</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>0</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -1192,13 +1217,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -1224,13 +1249,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>72</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1256,10 +1281,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C7" t="s">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
@@ -1285,10 +1313,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C8" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>0</x:v>
@@ -1314,10 +1345,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C9" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D9" t="b">
         <x:v>0</x:v>
@@ -1340,10 +1374,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" t="s">
-        <x:v>47</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C10" t="s">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D10" t="b">
         <x:v>0</x:v>
@@ -1366,10 +1403,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>67</x:v>
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C11" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D11" t="b">
         <x:v>1</x:v>
@@ -1392,10 +1432,10 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>63</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D12" t="b">
         <x:v>1</x:v>
@@ -1415,7 +1455,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D13" t="b">
         <x:v>1</x:v>
@@ -1432,10 +1472,10 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D14" t="b">
         <x:v>1</x:v>
@@ -1452,10 +1492,10 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D15" t="b">
         <x:v>1</x:v>
@@ -1472,10 +1512,10 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" t="b">
         <x:v>1</x:v>
@@ -1492,10 +1532,10 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D17" t="b">
         <x:v>1</x:v>
@@ -1512,10 +1552,10 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" t="s">
-        <x:v>1</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D18" t="b">
         <x:v>1</x:v>
@@ -1532,10 +1572,10 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>43</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D19" t="b">
         <x:v>1</x:v>
@@ -1552,10 +1592,10 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D20" t="b">
         <x:v>1</x:v>
@@ -1572,11 +1612,14 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B21" t="s">
         <x:v>36</x:v>
       </x:c>
+      <x:c r="C21" t="s">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="D21" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -1587,13 +1630,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H21">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J21">
         <x:v>2</x:v>
@@ -1607,10 +1650,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C22" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D22" t="b">
         <x:v>1</x:v>
@@ -1622,13 +1668,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H22">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J22">
         <x:v>2</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -14,246 +14,288 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="80">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="94">
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_IronPiece</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
     <x:t>Images/Icon_Image/Image_ChipCard</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 50 채워준다</x:t>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
   </x:si>
   <x:si>
     <x:t>괭이</x:t>
   </x:si>
   <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
     <x:t>옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Pumpkin</x:t>
   </x:si>
   <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_10</x:t>
+    <x:t>Item_Food_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Food_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Food_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Food_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Food_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_07</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_Can</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1056,7 +1098,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L22"/>
+  <x:dimension ref="A1:L35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="3" max="3" width="37.33203125" customWidth="1"/>
@@ -1071,127 +1113,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K3" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>52</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>65</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -1216,14 +1258,14 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
-      <x:c r="A5" s="3" t="s">
-        <x:v>63</x:v>
+      <x:c r="A5" s="1" t="s">
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>1</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -1248,14 +1290,14 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
-      <x:c r="A6" s="3" t="s">
-        <x:v>69</x:v>
+      <x:c r="A6" s="1" t="s">
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>0</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1280,14 +1322,14 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
-      <x:c r="A7" s="3" t="s">
-        <x:v>70</x:v>
+      <x:c r="A7" s="1" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>2</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
@@ -1312,14 +1354,14 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
-      <x:c r="A8" s="3" t="s">
-        <x:v>67</x:v>
+      <x:c r="A8" s="1" t="s">
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>0</x:v>
@@ -1345,13 +1387,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>61</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>78</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D9" t="b">
         <x:v>0</x:v>
@@ -1374,13 +1416,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" t="s">
-        <x:v>71</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>45</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D10" t="b">
         <x:v>0</x:v>
@@ -1403,13 +1445,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" t="s">
-        <x:v>62</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>4</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D11" t="b">
         <x:v>1</x:v>
@@ -1432,10 +1474,10 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" t="s">
-        <x:v>59</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>73</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D12" t="b">
         <x:v>1</x:v>
@@ -1452,10 +1494,10 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>35</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D13" t="b">
         <x:v>1</x:v>
@@ -1472,10 +1514,10 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>44</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D14" t="b">
         <x:v>1</x:v>
@@ -1492,10 +1534,10 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D15" t="b">
         <x:v>1</x:v>
@@ -1512,10 +1554,10 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D16" t="b">
         <x:v>1</x:v>
@@ -1532,10 +1574,10 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>32</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D17" t="b">
         <x:v>1</x:v>
@@ -1552,10 +1594,10 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" t="s">
-        <x:v>47</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>33</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D18" t="b">
         <x:v>1</x:v>
@@ -1572,10 +1614,10 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" t="b">
         <x:v>1</x:v>
@@ -1592,10 +1634,10 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D20" t="b">
         <x:v>1</x:v>
@@ -1612,13 +1654,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>36</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>77</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D21" t="b">
         <x:v>1</x:v>
@@ -1630,13 +1672,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H21">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J21">
         <x:v>2</x:v>
@@ -1650,13 +1692,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" t="s">
-        <x:v>58</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>40</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>6</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D22" t="b">
         <x:v>1</x:v>
@@ -1668,13 +1710,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>75</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H22">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J22">
         <x:v>2</x:v>
@@ -1684,6 +1726,151 @@
       </x:c>
       <x:c r="L22">
         <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:10" customHeight="1">
+      <x:c r="A31" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B31" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D31" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F31" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H31">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I31" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J31">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:10" customHeight="1">
+      <x:c r="A32" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B32" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F32" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H32">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I32" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J32">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:10" customHeight="1">
+      <x:c r="A33" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B33" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D33" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H33">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I33" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J33">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:10" customHeight="1">
+      <x:c r="A34" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B34" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F34" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H34">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I34" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J34">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:10" customHeight="1">
+      <x:c r="A35" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B35" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D35" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F35" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G35" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H35">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I35" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J35">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="9792"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="9768"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -14,288 +14,402 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="94">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="132">
+  <x:si>
+    <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pea</x:t>
+  </x:si>
   <x:si>
     <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Food_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Food_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Food_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Food_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Food_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Hoe</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1101,6 +1215,7 @@
   <x:dimension ref="A1:L35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
+    <x:col min="1" max="1" width="19.66796875" customWidth="1"/>
     <x:col min="3" max="3" width="37.33203125" customWidth="1"/>
     <x:col min="4" max="4" width="19.5703125" customWidth="1"/>
     <x:col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -1113,127 +1228,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J1" t="s">
-        <x:v>2</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>16</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>8</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>3</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K3" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>9</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -1259,13 +1374,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>53</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -1291,13 +1406,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>54</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1323,13 +1438,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>55</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
@@ -1355,13 +1470,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>0</x:v>
@@ -1387,13 +1502,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>82</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>70</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>93</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D9" t="b">
         <x:v>0</x:v>
@@ -1416,13 +1531,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" t="s">
-        <x:v>91</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>68</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D10" t="b">
         <x:v>0</x:v>
@@ -1445,13 +1560,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" t="s">
-        <x:v>86</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>48</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D11" t="b">
         <x:v>1</x:v>
@@ -1474,10 +1589,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" t="s">
-        <x:v>74</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>43</x:v>
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C12" t="s">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D12" t="b">
         <x:v>1</x:v>
@@ -1494,10 +1612,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" t="s">
-        <x:v>32</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" t="s">
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" t="b">
         <x:v>1</x:v>
@@ -1514,10 +1635,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B14" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="D14" t="b">
         <x:v>1</x:v>
@@ -1534,10 +1658,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" t="s">
-        <x:v>35</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>60</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D15" t="b">
         <x:v>1</x:v>
@@ -1554,10 +1681,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>59</x:v>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D16" t="b">
         <x:v>1</x:v>
@@ -1574,10 +1704,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" t="s">
-        <x:v>30</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>65</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C17" t="s">
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D17" t="b">
         <x:v>1</x:v>
@@ -1594,10 +1727,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" t="s">
-        <x:v>75</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C18" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D18" t="b">
         <x:v>1</x:v>
@@ -1614,10 +1750,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" t="s">
-        <x:v>29</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C19" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D19" t="b">
         <x:v>1</x:v>
@@ -1634,10 +1773,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D20" t="b">
         <x:v>1</x:v>
@@ -1654,13 +1796,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" t="s">
-        <x:v>79</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B21" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>92</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D21" t="b">
         <x:v>1</x:v>
@@ -1672,13 +1814,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>44</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H21">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>37</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J21">
         <x:v>2</x:v>
@@ -1692,13 +1834,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" t="s">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>62</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D22" t="b">
         <x:v>1</x:v>
@@ -1710,13 +1852,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H22">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>36</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J22">
         <x:v>2</x:v>
@@ -1728,12 +1870,199 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" spans="1:10" customHeight="1">
+      <x:c r="A23" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B23" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C23" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D23" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F23" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J23">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10" customHeight="1">
+      <x:c r="A24" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B24" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C24" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D24" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F24" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10" customHeight="1">
+      <x:c r="A25" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B25" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C25" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D25" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F25" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10" customHeight="1">
+      <x:c r="A26" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B26" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D26" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F26" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10" customHeight="1">
+      <x:c r="A27" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B27" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C27" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D27" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F27" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10" customHeight="1">
+      <x:c r="A28" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C28" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F28" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10" customHeight="1">
+      <x:c r="A29" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C29" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10" customHeight="1">
+      <x:c r="A30" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C30" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D30" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F30" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" t="s">
-        <x:v>90</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>69</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C31" t="s">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D31" t="b">
         <x:v>1</x:v>
@@ -1745,13 +2074,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" t="s">
-        <x:v>44</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H31">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" t="s">
-        <x:v>28</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J31">
         <x:v>0</x:v>
@@ -1759,10 +2088,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" t="s">
-        <x:v>76</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>66</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C32" t="s">
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D32" t="b">
         <x:v>1</x:v>
@@ -1774,13 +2106,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" t="s">
-        <x:v>44</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H32">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" t="s">
-        <x:v>27</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J32">
         <x:v>0</x:v>
@@ -1788,13 +2120,16 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>51</x:v>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C33" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D33" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E33">
         <x:v>1</x:v>
@@ -1803,13 +2138,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" t="s">
-        <x:v>44</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H33">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" t="s">
-        <x:v>26</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J33">
         <x:v>0</x:v>
@@ -1817,10 +2152,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" t="s">
-        <x:v>83</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>42</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C34" t="s">
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D34" t="b">
         <x:v>1</x:v>
@@ -1832,13 +2170,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" t="s">
-        <x:v>44</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H34">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" t="s">
-        <x:v>37</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J34">
         <x:v>0</x:v>
@@ -1846,13 +2184,16 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" t="s">
-        <x:v>84</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C35" t="s">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D35" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E35">
         <x:v>1</x:v>
@@ -1861,13 +2202,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" t="s">
-        <x:v>44</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H35">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J35">
         <x:v>0</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -14,402 +14,399 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="132">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="131">
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
+  </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
+    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Drop_04</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Drop_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Drop_08</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Drop_07</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
+    <x:t>Item_Seed_Onion</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Drop_06</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Craft_02</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
+    <x:t>Item_Seed_Pea</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Seed_Corn</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1228,127 +1225,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="J1" t="s">
-        <x:v>94</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>95</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L1" t="s">
-        <x:v>105</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J3" t="s">
-        <x:v>88</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K3" t="s">
-        <x:v>44</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="L3" t="s">
-        <x:v>51</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="3" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -1374,13 +1371,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -1406,13 +1403,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>76</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -1438,13 +1435,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>77</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
@@ -1470,13 +1467,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>0</x:v>
@@ -1502,13 +1499,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" t="s">
-        <x:v>58</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B9" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>128</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D9" t="b">
         <x:v>0</x:v>
@@ -1531,13 +1528,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" t="s">
-        <x:v>53</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B10" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D10" t="b">
         <x:v>0</x:v>
@@ -1560,13 +1557,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" t="s">
-        <x:v>52</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B11" t="s">
-        <x:v>107</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D11" t="b">
         <x:v>1</x:v>
@@ -1589,13 +1586,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" t="s">
-        <x:v>57</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>108</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>75</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D12" t="b">
         <x:v>1</x:v>
@@ -1612,13 +1609,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" t="s">
-        <x:v>91</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" t="s">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D13" t="b">
         <x:v>1</x:v>
@@ -1635,13 +1632,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B14" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>33</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D14" t="b">
         <x:v>1</x:v>
@@ -1658,13 +1655,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" t="s">
-        <x:v>99</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B15" t="s">
-        <x:v>19</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D15" t="b">
         <x:v>1</x:v>
@@ -1681,13 +1678,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" t="s">
-        <x:v>96</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>130</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D16" t="b">
         <x:v>1</x:v>
@@ -1704,13 +1701,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" t="s">
-        <x:v>86</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D17" t="b">
         <x:v>1</x:v>
@@ -1727,13 +1724,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" t="s">
-        <x:v>41</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D18" t="b">
         <x:v>1</x:v>
@@ -1750,13 +1747,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D19" t="b">
         <x:v>1</x:v>
@@ -1773,10 +1770,10 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C20" t="s">
         <x:v>30</x:v>
@@ -1796,13 +1793,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" t="s">
-        <x:v>49</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B21" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>129</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D21" t="b">
         <x:v>1</x:v>
@@ -1814,13 +1811,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" t="s">
-        <x:v>123</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H21">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>100</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J21">
         <x:v>2</x:v>
@@ -1834,13 +1831,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" t="s">
-        <x:v>45</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B22" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D22" t="b">
         <x:v>1</x:v>
@@ -1852,13 +1849,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" t="s">
-        <x:v>122</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H22">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I22" t="s">
-        <x:v>92</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J22">
         <x:v>2</x:v>
@@ -1872,13 +1869,13 @@
     </x:row>
     <x:row r="23" spans="1:10" customHeight="1">
       <x:c r="A23" t="s">
-        <x:v>68</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" t="s">
-        <x:v>121</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>73</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D23" t="b">
         <x:v>1</x:v>
@@ -1895,13 +1892,13 @@
     </x:row>
     <x:row r="24" spans="1:10" customHeight="1">
       <x:c r="A24" t="s">
-        <x:v>62</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B24" t="s">
-        <x:v>110</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>2</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D24" t="b">
         <x:v>1</x:v>
@@ -1918,13 +1915,13 @@
     </x:row>
     <x:row r="25" spans="1:10" customHeight="1">
       <x:c r="A25" t="s">
-        <x:v>60</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B25" t="s">
-        <x:v>119</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C25" t="s">
-        <x:v>3</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D25" t="b">
         <x:v>1</x:v>
@@ -1941,13 +1938,13 @@
     </x:row>
     <x:row r="26" spans="1:10" customHeight="1">
       <x:c r="A26" t="s">
-        <x:v>63</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B26" t="s">
-        <x:v>111</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C26" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D26" t="b">
         <x:v>1</x:v>
@@ -1964,13 +1961,13 @@
     </x:row>
     <x:row r="27" spans="1:10" customHeight="1">
       <x:c r="A27" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" t="s">
-        <x:v>127</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C27" t="s">
-        <x:v>72</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D27" t="b">
         <x:v>1</x:v>
@@ -1987,13 +1984,13 @@
     </x:row>
     <x:row r="28" spans="1:10" customHeight="1">
       <x:c r="A28" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>109</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>74</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D28" t="b">
         <x:v>1</x:v>
@@ -2010,13 +2007,13 @@
     </x:row>
     <x:row r="29" spans="1:10" customHeight="1">
       <x:c r="A29" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>118</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>0</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D29" t="b">
         <x:v>1</x:v>
@@ -2033,13 +2030,13 @@
     </x:row>
     <x:row r="30" spans="1:10" customHeight="1">
       <x:c r="A30" t="s">
-        <x:v>47</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>1</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D30" t="b">
         <x:v>1</x:v>
@@ -2056,13 +2053,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" t="s">
-        <x:v>59</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>78</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D31" t="b">
         <x:v>1</x:v>
@@ -2074,13 +2071,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" t="s">
-        <x:v>123</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H31">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" t="s">
-        <x:v>103</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J31">
         <x:v>0</x:v>
@@ -2088,13 +2085,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" t="s">
-        <x:v>64</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>81</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D32" t="b">
         <x:v>1</x:v>
@@ -2106,13 +2103,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" t="s">
-        <x:v>123</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H32">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" t="s">
-        <x:v>104</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J32">
         <x:v>0</x:v>
@@ -2120,13 +2117,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" t="s">
-        <x:v>65</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>106</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D33" t="b">
         <x:v>1</x:v>
@@ -2138,13 +2135,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" t="s">
-        <x:v>123</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H33">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J33">
         <x:v>0</x:v>
@@ -2152,13 +2149,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" t="s">
-        <x:v>50</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>120</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>80</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D34" t="b">
         <x:v>1</x:v>
@@ -2170,13 +2167,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" t="s">
-        <x:v>123</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H34">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" t="s">
-        <x:v>100</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="J34">
         <x:v>0</x:v>
@@ -2184,13 +2181,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" t="s">
-        <x:v>54</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D35" t="b">
         <x:v>1</x:v>
@@ -2202,13 +2199,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" t="s">
-        <x:v>123</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H35">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" t="s">
-        <x:v>48</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J35">
         <x:v>0</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12581"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BootCamp\JagalchiHang\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21060" windowHeight="6792"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="9768"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -21,73 +16,196 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="131">
   <x:si>
+    <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
     <x:t>갈증을 20 채워준다</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Seed_Potato</x:t>
@@ -99,91 +217,115 @@
     <x:t>Item_Seed_Carrot</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
+    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
   </x:si>
   <x:si>
+    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
     <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
   </x:si>
   <x:si>
     <x:t>UseItemType</x:t>
@@ -192,233 +334,86 @@
     <x:t>IsUsable</x:t>
   </x:si>
   <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
     <x:t>허기를 50 채워준다</x:t>
   </x:si>
   <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
     <x:t>Crop_Carrot</x:t>
   </x:si>
   <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
     <x:t>Crop_Tomato</x:t>
   </x:si>
   <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Pea</x:t>
   </x:si>
   <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
     <x:t>Crop_Wheat</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
     <x:t>Images/Icon_Image/lmage_Pea</x:t>
   </x:si>
   <x:si>
+    <x:t>Images/Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
     <x:t>Images/Icon_Image/Image_Can</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
+    <x:t>UseItemEffect</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -450,6 +445,11 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
@@ -464,23 +464,68 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:left>
       <x:right>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:right>
       <x:top>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -488,16 +533,16 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -505,15 +550,14 @@
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="12">
+  <x:dxfs count="30">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -596,7 +640,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -631,7 +674,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -676,7 +718,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -720,7 +761,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -728,10 +768,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -740,10 +780,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -755,10 +795,10 @@
           </x:font>
           <x:border>
             <x:left>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:left>
             <x:right>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:right>
             <x:top style="medium">
               <x:color rgb="ff6182d6"/>
@@ -767,10 +807,10 @@
               <x:color rgb="ff6182d6"/>
             </x:bottom>
             <x:vertical>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:vertical>
             <x:horizontal>
-              <x:color auto="1"/>
+              <x:color indexed="64"/>
             </x:horizontal>
           </x:border>
         </x:dxf>
@@ -805,7 +845,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -826,7 +865,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -857,15 +895,52 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
             <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
             <hs:offset val="0"/>
           </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
           <x:border>
-            <x:bottom style="medium">
-              <x:color rgb="ff6182d6"/>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
             </x:bottom>
           </x:border>
         </x:dxf>
@@ -873,16 +948,429 @@
       <mc:Fallback>
         <x:dxf>
           <x:font>
-            <x:b val="1"/>
-          </x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
           <x:border>
-            <x:bottom style="medium">
-              <x:color rgb="ff6182d6"/>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
             </x:bottom>
           </x:border>
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:left style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:left>
+        <x:right style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:right>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -911,7 +1399,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1123,127 +1611,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>121</x:v>
-      </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:12" ht="12.300000000000001">
+      <x:c r="A2" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:12" ht="12.300000000000001">
+      <x:c r="A3" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:12" ht="13.199999999999999">
-      <x:c r="A2" s="4" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:12" ht="13.199999999999999">
-      <x:c r="A3" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
         <x:v>130</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:12" ht="13.199999999999999">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1267,15 +1755,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:12" ht="13.199999999999999">
+    <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1299,15 +1787,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:12" ht="13.199999999999999">
+    <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1331,15 +1819,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:12" ht="13.199999999999999">
+    <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1363,15 +1851,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:12" ht="13.199999999999999">
+    <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1397,13 +1885,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1426,13 +1914,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>0</x:v>
@@ -1455,13 +1943,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -1484,13 +1972,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -1507,13 +1995,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -1530,13 +2018,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
@@ -1553,13 +2041,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -1576,13 +2064,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -1599,13 +2087,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -1622,13 +2110,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -1645,13 +2133,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -1668,13 +2156,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -1691,13 +2179,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D21" s="1" t="b">
         <x:v>1</x:v>
@@ -1709,13 +2197,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -1729,13 +2217,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -1747,13 +2235,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -1767,13 +2255,13 @@
     </x:row>
     <x:row r="23" spans="1:10" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -1790,13 +2278,13 @@
     </x:row>
     <x:row r="24" spans="1:10" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D24" s="1" t="b">
         <x:v>1</x:v>
@@ -1813,13 +2301,13 @@
     </x:row>
     <x:row r="25" spans="1:10" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -1836,13 +2324,13 @@
     </x:row>
     <x:row r="26" spans="1:10" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -1859,13 +2347,13 @@
     </x:row>
     <x:row r="27" spans="1:10" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -1882,13 +2370,13 @@
     </x:row>
     <x:row r="28" spans="1:10" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -1905,13 +2393,13 @@
     </x:row>
     <x:row r="29" spans="1:10" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -1928,13 +2416,13 @@
     </x:row>
     <x:row r="30" spans="1:10" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -1951,13 +2439,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -1969,13 +2457,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -1983,13 +2471,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2001,13 +2489,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2015,13 +2503,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D33" s="1" t="b">
         <x:v>1</x:v>
@@ -2033,13 +2521,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2047,13 +2535,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2065,13 +2553,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2079,13 +2567,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2097,13 +2585,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="J35" s="1">
         <x:v>0</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="9768"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="10872"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -14,399 +14,417 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="131">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="137">
+  <x:si>
+    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_BagNpc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Battle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
+  </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
   </x:si>
   <x:si>
+    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Bag_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_BattleNpc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
     <x:t>감자</x:t>
   </x:si>
   <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
+    <x:t>완두콩</x:t>
   </x:si>
   <x:si>
     <x:t>통조림</x:t>
   </x:si>
   <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
     <x:t>호박</x:t>
   </x:si>
   <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
   </x:si>
   <x:si>
     <x:t>콩떡</x:t>
   </x:si>
   <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
     <x:t>토마토</x:t>
   </x:si>
   <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
     <x:t>막대기</x:t>
   </x:si>
   <x:si>
     <x:t>감자전</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
+    <x:t>UseItemEffect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Seed_Onion</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Drop_04</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Drop_02</x:t>
   </x:si>
   <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>아이템 사용 효과 설명</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
+    <x:t>Item_Drop_08</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Drop_07</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
+    <x:t>Images/Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Can</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/lmage_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemEffect</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -558,6 +576,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -640,6 +659,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -674,6 +694,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -718,6 +739,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -761,6 +783,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -845,6 +868,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -865,6 +889,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -895,6 +920,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1595,7 +1621,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L35"/>
+  <x:dimension ref="A1:L37"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.66796875" style="1" customWidth="1"/>
@@ -1614,124 +1640,124 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>130</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1757,13 +1783,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1789,13 +1815,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1821,13 +1847,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1853,13 +1879,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1885,13 +1911,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1914,13 +1940,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>0</x:v>
@@ -1943,13 +1969,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -1972,13 +1998,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -1995,13 +2021,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -2018,13 +2044,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
@@ -2041,13 +2067,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -2064,13 +2090,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -2087,13 +2113,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -2110,13 +2136,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -2133,13 +2159,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -2156,13 +2182,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -2179,13 +2205,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D21" s="1" t="b">
         <x:v>1</x:v>
@@ -2197,13 +2223,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -2217,13 +2243,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -2235,13 +2261,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -2255,13 +2281,13 @@
     </x:row>
     <x:row r="23" spans="1:10" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -2278,13 +2304,13 @@
     </x:row>
     <x:row r="24" spans="1:10" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D24" s="1" t="b">
         <x:v>1</x:v>
@@ -2301,13 +2327,13 @@
     </x:row>
     <x:row r="25" spans="1:10" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -2324,13 +2350,13 @@
     </x:row>
     <x:row r="26" spans="1:10" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -2347,13 +2373,13 @@
     </x:row>
     <x:row r="27" spans="1:10" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -2370,13 +2396,13 @@
     </x:row>
     <x:row r="28" spans="1:10" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -2393,13 +2419,13 @@
     </x:row>
     <x:row r="29" spans="1:10" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -2416,13 +2442,13 @@
     </x:row>
     <x:row r="30" spans="1:10" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -2439,13 +2465,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -2457,13 +2483,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -2471,13 +2497,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2489,13 +2515,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2503,13 +2529,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D33" s="1" t="b">
         <x:v>1</x:v>
@@ -2521,13 +2547,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2535,13 +2561,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2553,13 +2579,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2567,13 +2593,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2585,15 +2611,61 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="J35" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:10" customHeight="1">
+      <x:c r="A36" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B36" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:10" customHeight="1">
+      <x:c r="A37" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
+  <x:fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\GoToSeven\JagalchiHang\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="9768"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294938660" windowHeight="16530"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -16,67 +21,367 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="131">
   <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemEffect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
     <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
   </x:si>
   <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
+    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/lmage_Wheat</x:t>
@@ -85,335 +390,35 @@
     <x:t>Images/Icon_Image/Image_Water</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 20 채워준다</x:t>
+    <x:t>UseItemDescription</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Seed_Pumpkin</x:t>
   </x:si>
   <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Seed_Potato</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Seed_Tomato</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
+    <x:t>Images/Icon_Image/Image_Can</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/lmage_Pea</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemEffect</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -445,11 +450,6 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
-      <x:name val="돋움"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
@@ -464,7 +464,7 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border diagonalUp="1" diagonalDown="1">
+    <x:border>
       <x:left>
         <x:color indexed="64"/>
       </x:left>
@@ -477,55 +477,10 @@
       <x:bottom>
         <x:color indexed="64"/>
       </x:bottom>
-      <x:diagonal>
-        <x:color indexed="64"/>
-      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="15">
+  <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -539,7 +494,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -550,9 +505,9 @@
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle xfId="0" builtinId="0"/>
+    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="30">
+  <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:dxf hs:applyExtension="1">
@@ -920,457 +875,6 @@
         </x:dxf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ffd9e6fd"/>
-              <x:bgColor rgb="ffd9e6fd"/>
-            </x:patternFill>
-          </x:fill>
-          <x:border>
-            <x:bottom style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:bottom>
-          </x:border>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ffd9e6fd"/>
-              <x:bgColor rgb="ffd9e6fd"/>
-            </x:patternFill>
-          </x:fill>
-          <x:border>
-            <x:bottom style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:bottom>
-          </x:border>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ffd9e6fd"/>
-              <x:bgColor rgb="ffd9e6fd"/>
-            </x:patternFill>
-          </x:fill>
-          <x:border>
-            <x:top style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:top>
-          </x:border>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ffd9e6fd"/>
-              <x:bgColor rgb="ffd9e6fd"/>
-            </x:patternFill>
-          </x:fill>
-          <x:border>
-            <x:top style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:top>
-          </x:border>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:fgColor rgb="ffd9d9d9"/>
-          <x:bgColor rgb="ffd9d9d9"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:fgColor rgb="ffd9d9d9"/>
-          <x:bgColor rgb="ffd9d9d9"/>
-        </x:patternFill>
-      </x:fill>
-      <x:border>
-        <x:left style="thin">
-          <x:color rgb="ffbfbfbf"/>
-        </x:left>
-        <x:right style="thin">
-          <x:color rgb="ffbfbfbf"/>
-        </x:right>
-      </x:border>
-    </x:dxf>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:fgColor rgb="ffd9d9d9"/>
-          <x:bgColor rgb="ffd9d9d9"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:border>
-            <x:top style="thin">
-              <x:color rgb="ff4285f4"/>
-            </x:top>
-            <x:bottom style="thin">
-              <x:color rgb="ff4285f4"/>
-            </x:bottom>
-          </x:border>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-          <x:border>
-            <x:top style="thin">
-              <x:color rgb="ff4285f4"/>
-            </x:top>
-            <x:bottom style="thin">
-              <x:color rgb="ff4285f4"/>
-            </x:bottom>
-          </x:border>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:border>
-            <x:bottom style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:bottom>
-          </x:border>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-          <x:border>
-            <x:bottom style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:bottom>
-          </x:border>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:fgColor rgb="ffd9e6fd"/>
-          <x:bgColor rgb="ffd9e6fd"/>
-        </x:patternFill>
-      </x:fill>
-      <x:border>
-        <x:bottom style="thin">
-          <x:color rgb="ff8db6f9"/>
-        </x:bottom>
-      </x:border>
-    </x:dxf>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:fgColor rgb="ffd9e6fd"/>
-          <x:bgColor rgb="ffd9e6fd"/>
-        </x:patternFill>
-      </x:fill>
-      <x:border>
-        <x:bottom style="thin">
-          <x:color rgb="ff8db6f9"/>
-        </x:bottom>
-      </x:border>
-    </x:dxf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:border>
-            <x:left style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:left>
-            <x:right style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:right>
-            <x:top style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:top>
-            <x:bottom style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:bottom>
-            <x:horizontal style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:horizontal>
-          </x:border>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-          </x:font>
-          <x:border>
-            <x:left style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:left>
-            <x:right style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:right>
-            <x:top style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:top>
-            <x:bottom style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:bottom>
-            <x:horizontal style="thin">
-              <x:color rgb="ff8db6f9"/>
-            </x:horizontal>
-          </x:border>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ffffffff"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ff4285f4"/>
-              <x:bgColor rgb="ff4285f4"/>
-            </x:patternFill>
-          </x:fill>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ffffffff"/>
-            <x:b val="1"/>
-          </x:font>
-          <x:fill>
-            <x:patternFill patternType="solid">
-              <x:fgColor rgb="ff4285f4"/>
-              <x:bgColor rgb="ff4285f4"/>
-            </x:patternFill>
-          </x:fill>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-          <x:border>
-            <x:top style="double">
-              <x:color rgb="ff4285f4"/>
-            </x:top>
-          </x:border>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-          <x:border>
-            <x:top style="double">
-              <x:color rgb="ff4285f4"/>
-            </x:top>
-          </x:border>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:dxf hs:applyExtension="1">
-          <x:font hs:extension="1">
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
-            <hs:size val="0"/>
-            <hs:ratio val="0"/>
-            <hs:spacing val="0"/>
-            <hs:offset val="0"/>
-          </x:font>
-        </x:dxf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:dxf>
-          <x:font>
-            <x:color rgb="ff000000"/>
-            <x:b val="1"/>
-          </x:font>
-        </x:dxf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:fgColor rgb="ffd9e6fd"/>
-          <x:bgColor rgb="ffd9e6fd"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:fgColor rgb="ffd9e6fd"/>
-          <x:bgColor rgb="ffd9e6fd"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
   </x:dxfs>
   <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
@@ -1399,7 +903,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1611,127 +1115,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:12" ht="13.199999999999999">
+      <x:c r="A2" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:12" ht="13.199999999999999">
+      <x:c r="A3" s="4" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:12" ht="12.300000000000001">
-      <x:c r="A2" s="4" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:12" ht="12.300000000000001">
-      <x:c r="A3" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="G3" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H3" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I3" s="2" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
+      <x:c r="J3" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K3" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L3" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:12" ht="13.199999999999999">
+      <x:c r="A4" s="4" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="H3" s="2" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="I3" s="2" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="J3" s="1" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="K3" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="L3" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:12" ht="12.300000000000001">
-      <x:c r="A4" s="4" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1755,15 +1259,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:12" ht="12.300000000000001">
+    <x:row r="5" spans="1:12" ht="13.199999999999999">
       <x:c r="A5" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1787,15 +1291,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:12" ht="12.300000000000001">
+    <x:row r="6" spans="1:12" ht="13.199999999999999">
       <x:c r="A6" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1819,15 +1323,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:12" ht="12.300000000000001">
+    <x:row r="7" spans="1:12" ht="13.199999999999999">
       <x:c r="A7" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1851,15 +1355,15 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:12" ht="12.300000000000001">
+    <x:row r="8" spans="1:12" ht="13.199999999999999">
       <x:c r="A8" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1885,13 +1389,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1914,13 +1418,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>0</x:v>
@@ -1943,13 +1447,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -1972,13 +1476,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -1995,13 +1499,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -2018,13 +1522,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
@@ -2041,13 +1545,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -2064,13 +1568,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -2087,13 +1591,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -2110,13 +1614,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -2133,13 +1637,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -2156,13 +1660,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -2179,13 +1683,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D21" s="1" t="b">
         <x:v>1</x:v>
@@ -2197,13 +1701,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -2217,13 +1721,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -2235,13 +1739,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -2255,13 +1759,13 @@
     </x:row>
     <x:row r="23" spans="1:10" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -2278,13 +1782,13 @@
     </x:row>
     <x:row r="24" spans="1:10" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D24" s="1" t="b">
         <x:v>1</x:v>
@@ -2301,13 +1805,13 @@
     </x:row>
     <x:row r="25" spans="1:10" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -2324,13 +1828,13 @@
     </x:row>
     <x:row r="26" spans="1:10" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -2347,13 +1851,13 @@
     </x:row>
     <x:row r="27" spans="1:10" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -2370,13 +1874,13 @@
     </x:row>
     <x:row r="28" spans="1:10" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -2393,13 +1897,13 @@
     </x:row>
     <x:row r="29" spans="1:10" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -2416,13 +1920,13 @@
     </x:row>
     <x:row r="30" spans="1:10" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -2439,13 +1943,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -2457,13 +1961,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -2471,13 +1975,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2489,13 +1993,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2503,31 +2007,31 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E33" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2535,13 +2039,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2553,13 +2057,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2567,13 +2071,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2585,13 +2089,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J35" s="1">
         <x:v>0</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23580" windowHeight="10872"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23556" windowHeight="10944"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -14,342 +14,366 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="137">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="140">
+  <x:si>
+    <x:t>전기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_BattleNpc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Battle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Bag_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
+    <x:t>Item_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/Image_BagNpc</x:t>
   </x:si>
   <x:si>
-    <x:t>Npc_Battle_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가방 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투 Npc</x:t>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
   </x:si>
   <x:si>
     <x:t>UseItemType</x:t>
   </x:si>
   <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
     <x:t>IsUsable</x:t>
   </x:si>
   <x:si>
     <x:t>IsStackable</x:t>
   </x:si>
   <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
     <x:t>아이템 사용 효과</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Bag_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_BattleNpc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
+    <x:t>Images/Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/Image_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
   </x:si>
   <x:si>
     <x:t>UseItemEffect</x:t>
@@ -358,51 +382,48 @@
     <x:t>Item_Drop_03</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Seed_Wheat</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Seed_Pea</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Drop_10</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Pumpkin</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Seed_Corn</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Drop_02</x:t>
   </x:si>
   <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
     <x:t>MinDropCount</x:t>
   </x:si>
   <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Drop_09</x:t>
   </x:si>
   <x:si>
@@ -412,19 +433,7 @@
     <x:t>아이템 사용 효과 설명</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Drop_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pea</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -576,7 +585,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -659,7 +667,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -694,7 +701,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -739,7 +745,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -783,7 +788,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -868,7 +872,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -889,7 +892,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -920,7 +922,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1621,7 +1622,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L37"/>
+  <x:dimension ref="A1:L38"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.66796875" style="1" customWidth="1"/>
@@ -1637,127 +1638,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1783,13 +1784,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1815,13 +1816,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1847,13 +1848,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1879,13 +1880,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1911,13 +1912,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1940,13 +1941,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>0</x:v>
@@ -1969,13 +1970,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -1998,13 +1999,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -2021,13 +2022,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -2044,10 +2045,10 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>74</x:v>
@@ -2067,13 +2068,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -2090,13 +2091,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -2113,13 +2114,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -2136,13 +2137,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -2159,13 +2160,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -2182,13 +2183,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -2205,13 +2206,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D21" s="1" t="b">
         <x:v>1</x:v>
@@ -2223,13 +2224,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -2243,13 +2244,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -2261,13 +2262,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -2281,13 +2282,13 @@
     </x:row>
     <x:row r="23" spans="1:10" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -2304,13 +2305,13 @@
     </x:row>
     <x:row r="24" spans="1:10" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D24" s="1" t="b">
         <x:v>1</x:v>
@@ -2327,13 +2328,13 @@
     </x:row>
     <x:row r="25" spans="1:10" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -2350,13 +2351,13 @@
     </x:row>
     <x:row r="26" spans="1:10" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -2373,13 +2374,13 @@
     </x:row>
     <x:row r="27" spans="1:10" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -2396,13 +2397,13 @@
     </x:row>
     <x:row r="28" spans="1:10" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -2419,13 +2420,13 @@
     </x:row>
     <x:row r="29" spans="1:10" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -2442,13 +2443,13 @@
     </x:row>
     <x:row r="30" spans="1:10" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -2465,13 +2466,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -2483,13 +2484,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -2497,13 +2498,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2515,13 +2516,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2529,13 +2530,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D33" s="1" t="b">
         <x:v>1</x:v>
@@ -2547,13 +2548,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2561,13 +2562,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2579,13 +2580,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2593,13 +2594,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2611,13 +2612,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="J35" s="1">
         <x:v>0</x:v>
@@ -2625,13 +2626,13 @@
     </x:row>
     <x:row r="36" spans="1:10" customHeight="1">
       <x:c r="A36" t="s">
-        <x:v>3</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D36" s="1" t="b">
         <x:v>0</x:v>
@@ -2648,13 +2649,13 @@
     </x:row>
     <x:row r="37" spans="1:10" customHeight="1">
       <x:c r="A37" t="s">
-        <x:v>70</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D37" s="1" t="b">
         <x:v>0</x:v>
@@ -2666,6 +2667,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:10" customHeight="1">
+      <x:c r="A38" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B38" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -16,424 +16,424 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="140">
   <x:si>
+    <x:t>Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
     <x:t>전기</x:t>
   </x:si>
   <x:si>
-    <x:t>Images/Icon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OnionSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_TomatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_BattleNpc</x:t>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maIcon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Bag_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Battle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Craft_05</x:t>
   </x:si>
   <x:si>
+    <x:t>UseItemEffect</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Craft_01</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Battle_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Craft_04</x:t>
   </x:si>
   <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Bag_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Doenjangjjigae</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가방 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_BagNpc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/Image_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemEffect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_06</x:t>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
   </x:si>
   <x:si>
     <x:t>아이템 슬롯 중복 가능 여부</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Drop_10</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
     <x:t>아이템 사용 가능 여부</x:t>
   </x:si>
   <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Drop_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_TomatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_KongTteog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_OnionSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Bag</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Hoe</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -585,6 +585,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -667,6 +668,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -701,6 +703,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -745,6 +748,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -788,6 +792,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -872,6 +877,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -892,6 +898,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -922,6 +929,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1638,40 +1646,40 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>124</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
@@ -1685,80 +1693,80 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1784,13 +1792,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1816,13 +1824,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1848,13 +1856,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1880,13 +1888,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1912,13 +1920,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1941,13 +1949,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>0</x:v>
@@ -1970,13 +1978,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -1999,13 +2007,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -2022,13 +2030,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -2045,13 +2053,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
@@ -2068,13 +2076,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -2091,13 +2099,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -2114,13 +2122,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -2137,13 +2145,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -2160,13 +2168,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -2183,13 +2191,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -2206,13 +2214,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D21" s="1" t="b">
         <x:v>1</x:v>
@@ -2224,13 +2232,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -2244,13 +2252,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -2262,13 +2270,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -2282,13 +2290,13 @@
     </x:row>
     <x:row r="23" spans="1:10" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -2305,13 +2313,13 @@
     </x:row>
     <x:row r="24" spans="1:10" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D24" s="1" t="b">
         <x:v>1</x:v>
@@ -2328,13 +2336,13 @@
     </x:row>
     <x:row r="25" spans="1:10" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -2351,13 +2359,13 @@
     </x:row>
     <x:row r="26" spans="1:10" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -2374,13 +2382,13 @@
     </x:row>
     <x:row r="27" spans="1:10" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -2397,13 +2405,13 @@
     </x:row>
     <x:row r="28" spans="1:10" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -2420,13 +2428,13 @@
     </x:row>
     <x:row r="29" spans="1:10" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -2443,13 +2451,13 @@
     </x:row>
     <x:row r="30" spans="1:10" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -2466,13 +2474,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -2484,13 +2492,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -2498,13 +2506,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2516,13 +2524,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2530,13 +2538,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D33" s="1" t="b">
         <x:v>1</x:v>
@@ -2548,13 +2556,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2562,13 +2570,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2580,13 +2588,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2594,13 +2602,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2612,13 +2620,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J35" s="1">
         <x:v>0</x:v>
@@ -2626,13 +2634,13 @@
     </x:row>
     <x:row r="36" spans="1:10" customHeight="1">
       <x:c r="A36" t="s">
-        <x:v>22</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D36" s="1" t="b">
         <x:v>0</x:v>
@@ -2649,13 +2657,13 @@
     </x:row>
     <x:row r="37" spans="1:10" customHeight="1">
       <x:c r="A37" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>61</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D37" s="1" t="b">
         <x:v>0</x:v>
@@ -2672,13 +2680,13 @@
     </x:row>
     <x:row r="38" spans="1:10" customHeight="1">
       <x:c r="A38" t="s">
-        <x:v>31</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D38" s="1" t="b">
         <x:v>0</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -14,426 +14,435 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="140">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="143">
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Bag_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_FarmPlot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Battle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_FarmPlot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밭 증축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maIcon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemEffect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_TomatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_KongTteog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_OnionSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Water</x:t>
+  </x:si>
   <x:si>
     <x:t>Icon_Image/lmage_Tomato</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Doenjangjjigae</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
+    <x:t>Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Bag</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Hoe</x:t>
   </x:si>
   <x:si>
     <x:t>Icon_Image/lmage_Wheat</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maIcon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가방 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Bag_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Battle_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemEffect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_TomatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_OnionSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon_Image/lmage_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Bag</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Hoe</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -585,7 +594,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -668,7 +676,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -703,7 +710,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -748,7 +754,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -792,7 +797,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -877,7 +881,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -898,7 +901,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -929,7 +931,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1630,7 +1631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L38"/>
+  <x:dimension ref="A1:L39"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.66796875" style="1" customWidth="1"/>
@@ -1646,127 +1647,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I3" s="2" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="J3" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K3" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="L3" s="1" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="I3" s="2" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="J3" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K3" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="L3" s="1" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>132</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1792,13 +1793,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1824,13 +1825,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1856,13 +1857,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1888,13 +1889,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1920,13 +1921,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1949,10 +1950,10 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>128</x:v>
@@ -1978,13 +1979,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -2007,13 +2008,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -2030,13 +2031,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -2053,13 +2054,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
@@ -2076,13 +2077,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -2099,13 +2100,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -2122,13 +2123,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -2148,10 +2149,10 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -2168,13 +2169,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -2191,13 +2192,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -2214,10 +2215,10 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>138</x:v>
@@ -2232,13 +2233,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -2252,13 +2253,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -2270,13 +2271,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -2290,13 +2291,13 @@
     </x:row>
     <x:row r="23" spans="1:10" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -2313,10 +2314,10 @@
     </x:row>
     <x:row r="24" spans="1:10" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>120</x:v>
@@ -2336,13 +2337,13 @@
     </x:row>
     <x:row r="25" spans="1:10" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -2359,13 +2360,13 @@
     </x:row>
     <x:row r="26" spans="1:10" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -2382,13 +2383,13 @@
     </x:row>
     <x:row r="27" spans="1:10" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -2405,13 +2406,13 @@
     </x:row>
     <x:row r="28" spans="1:10" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -2428,13 +2429,13 @@
     </x:row>
     <x:row r="29" spans="1:10" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -2451,13 +2452,13 @@
     </x:row>
     <x:row r="30" spans="1:10" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -2474,13 +2475,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -2492,13 +2493,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -2506,13 +2507,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2524,13 +2525,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2538,13 +2539,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D33" s="1" t="b">
         <x:v>1</x:v>
@@ -2556,13 +2557,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2570,13 +2571,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2588,13 +2589,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2602,13 +2603,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2620,13 +2621,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="J35" s="1">
         <x:v>0</x:v>
@@ -2634,13 +2635,13 @@
     </x:row>
     <x:row r="36" spans="1:10" customHeight="1">
       <x:c r="A36" t="s">
-        <x:v>94</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D36" s="1" t="b">
         <x:v>0</x:v>
@@ -2657,13 +2658,13 @@
     </x:row>
     <x:row r="37" spans="1:10" customHeight="1">
       <x:c r="A37" t="s">
-        <x:v>56</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>47</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D37" s="1" t="b">
         <x:v>0</x:v>
@@ -2680,13 +2681,13 @@
     </x:row>
     <x:row r="38" spans="1:10" customHeight="1">
       <x:c r="A38" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>4</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D38" s="1" t="b">
         <x:v>0</x:v>
@@ -2698,6 +2699,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:10" customHeight="1">
+      <x:c r="A39" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="23556" windowHeight="10944"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="30492" windowHeight="12792"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -16,433 +16,433 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="143">
   <x:si>
+    <x:t>Icon_Image/Image_TomatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Crowbar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_KongTteog</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_OnionSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_WheatSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Kalgugsu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Flipper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_IronPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_WoodPiece</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Bag</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Battle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_FarmPlot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemEffect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
     <x:t>아이디</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maIcon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밭 증축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
   </x:si>
   <x:si>
     <x:t>Npc_Bag_01</x:t>
   </x:si>
   <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
     <x:t>ItemName</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_FarmPlot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Battle_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_04</x:t>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
   </x:si>
   <x:si>
     <x:t>Icon_Image/Image_FarmPlot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밭 증축</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가방 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maIcon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Doenjangjjigae</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemEffect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_TomatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Crowbar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_WheatSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_CornSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_KongTteog</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Kalgugsu</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_OnionSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Flipper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Bag</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Pea</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -594,6 +594,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -676,6 +677,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -710,6 +712,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -754,6 +757,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -797,6 +801,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -881,6 +886,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -901,6 +907,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -931,6 +938,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1647,127 +1655,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>109</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1793,13 +1801,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1825,13 +1833,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1857,13 +1865,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1889,13 +1897,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1921,13 +1929,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1950,13 +1958,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>0</x:v>
@@ -1979,13 +1987,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -2008,13 +2016,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -2031,13 +2039,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -2054,13 +2062,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
@@ -2077,13 +2085,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -2100,13 +2108,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -2123,13 +2131,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -2146,13 +2154,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -2169,13 +2177,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -2192,13 +2200,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -2215,13 +2223,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D21" s="1" t="b">
         <x:v>1</x:v>
@@ -2233,13 +2241,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -2253,13 +2261,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -2271,13 +2279,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -2289,15 +2297,15 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:10" customHeight="1">
+    <x:row r="23" spans="1:12" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -2309,18 +2317,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:10" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K23" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L23" s="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:12" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D24" s="1" t="b">
         <x:v>1</x:v>
@@ -2332,18 +2346,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J24" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:10" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K24" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L24" s="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:12" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -2355,18 +2375,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J25" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:10" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K25" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L25" s="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:12" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -2378,18 +2404,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:10" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K26" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L26" s="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:12" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -2401,18 +2433,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J27" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:10" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K27" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L27" s="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:12" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -2424,18 +2462,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:10" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K28" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L28" s="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:12" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -2447,18 +2491,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J29" s="1">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:10" customHeight="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K29" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L29" s="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:12" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -2470,18 +2520,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J30" s="1">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K30" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L30" s="1">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -2493,13 +2549,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -2507,13 +2563,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2525,13 +2581,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2539,13 +2595,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D33" s="1" t="b">
         <x:v>1</x:v>
@@ -2557,13 +2613,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2571,13 +2627,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2589,13 +2645,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2603,13 +2659,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2621,13 +2677,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J35" s="1">
         <x:v>0</x:v>
@@ -2635,13 +2691,13 @@
     </x:row>
     <x:row r="36" spans="1:10" customHeight="1">
       <x:c r="A36" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>51</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D36" s="1" t="b">
         <x:v>0</x:v>
@@ -2658,13 +2714,13 @@
     </x:row>
     <x:row r="37" spans="1:10" customHeight="1">
       <x:c r="A37" t="s">
-        <x:v>3</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>59</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D37" s="1" t="b">
         <x:v>0</x:v>
@@ -2681,13 +2737,13 @@
     </x:row>
     <x:row r="38" spans="1:10" customHeight="1">
       <x:c r="A38" t="s">
-        <x:v>88</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D38" s="1" t="b">
         <x:v>0</x:v>
@@ -2704,13 +2760,13 @@
     </x:row>
     <x:row r="39" spans="1:10" customHeight="1">
       <x:c r="A39" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>17</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D39" s="1" t="b">
         <x:v>0</x:v>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="30492" windowHeight="12792"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="23556" windowHeight="10944"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -16,430 +16,430 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="143">
   <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemDescription</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Battle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_FarmPlot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Craft_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 100 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemEffect</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MinDropCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Drop_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 슬롯 중복 가능 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>된장찌개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 고로케</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공업용 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밭 증축</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 조각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식물성 기름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thirsty</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hunger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>가방 Npc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전자 칩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수 씨앗</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Npc_Bag_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 종류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 10 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 등장 가중치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsStackable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 30 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최대 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이템 사용 효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropWeight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허기를 50 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈증을 20 채워준다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스폰 최소 수량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsUsable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_VegetableOil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Doenjangjjigae</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_GamjaGoloke</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_PumpkinSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>maIcon_Image/Image_WoodStick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칼국수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>괭이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뒤짚개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통조림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콩떡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>막대기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Hoe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Bag</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Battle</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Can</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Water</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon_Image/Image_TomatoSeed</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon_Image/Image_PotatoSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Imgae_Gamjajeon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CornSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_ChipCard</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon_Image/Image_Crowbar</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon_Image/Imgae_Gamjajeon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_CornSeed</x:t>
+    <x:t>Icon_Image/Image_OnionSeed</x:t>
   </x:si>
   <x:si>
     <x:t>Icon_Image/Image_KongTteog</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon_Image/Image_ChipCard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_OnionSeed</x:t>
+    <x:t>Icon_Image/Image_OilTank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_CarrotSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_Flipper</x:t>
   </x:si>
   <x:si>
     <x:t>Icon_Image/Image_WheatSeed</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PotatoSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_OilTank</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon_Image/Image_Kalgugsu</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon_Image/Image_CarrotSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Flipper</x:t>
+    <x:t>Icon_Image/Image_PeaSeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Image/Image_WoodPiece</x:t>
   </x:si>
   <x:si>
     <x:t>Icon_Image/Image_IronPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PeaSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_WoodPiece</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Hoe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Bag</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Water</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Can</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Battle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemDescription</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Battle_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_FarmPlot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Craft_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 100 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemEffect</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MinDropCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Drop_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 슬롯 중복 가능 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칼국수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>괭이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>막대기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통조림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콩떡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>뒤짚개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>maIcon_Image/Image_WoodStick</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Electricity</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_VegetableOil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_Doenjangjjigae</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_GamjaGoloke</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Image/Image_PumpkinSeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밭 증축</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공업용 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 고로케</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>된장찌개</x:t>
-  </x:si>
-  <x:si>
-    <x:t>식물성 기름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전자 칩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>양파 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전투 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hunger</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 조각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>가방 Npc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀 씨앗</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thirsty</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Npc_Bag_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 종류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 10 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 30 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 등장 가중치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 50 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이템 사용 효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최대 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허기를 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsStackable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>갈증을 20 채워준다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 최소 수량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IsUsable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
   </x:si>
   <x:si>
     <x:t>Icon_Image/Image_FarmPlot</x:t>
@@ -594,7 +594,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -677,7 +676,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -712,7 +710,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -757,7 +754,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -801,7 +797,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -886,7 +881,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -907,7 +901,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -938,7 +931,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1655,127 +1647,127 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" customHeight="1">
       <x:c r="A1" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>118</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="12.300000000000001">
       <x:c r="A2" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" ht="12.300000000000001">
       <x:c r="A3" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>120</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:12" ht="12.300000000000001">
       <x:c r="A4" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D4" s="2" t="b">
         <x:v>1</x:v>
@@ -1801,13 +1793,13 @@
     </x:row>
     <x:row r="5" spans="1:12" ht="12.300000000000001">
       <x:c r="A5" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D5" s="2" t="b">
         <x:v>1</x:v>
@@ -1833,13 +1825,13 @@
     </x:row>
     <x:row r="6" spans="1:12" ht="12.300000000000001">
       <x:c r="A6" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D6" s="2" t="b">
         <x:v>1</x:v>
@@ -1865,13 +1857,13 @@
     </x:row>
     <x:row r="7" spans="1:12" ht="12.300000000000001">
       <x:c r="A7" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D7" s="2" t="b">
         <x:v>1</x:v>
@@ -1897,13 +1889,13 @@
     </x:row>
     <x:row r="8" spans="1:12" ht="12.300000000000001">
       <x:c r="A8" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D8" s="2" t="b">
         <x:v>0</x:v>
@@ -1929,13 +1921,13 @@
     </x:row>
     <x:row r="9" spans="1:12" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>0</x:v>
@@ -1958,13 +1950,13 @@
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>0</x:v>
@@ -1976,7 +1968,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="1">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K10" s="1">
         <x:v>1</x:v>
@@ -1987,13 +1979,13 @@
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -2016,13 +2008,13 @@
     </x:row>
     <x:row r="12" spans="1:10" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
@@ -2039,13 +2031,13 @@
     </x:row>
     <x:row r="13" spans="1:10" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
@@ -2062,13 +2054,13 @@
     </x:row>
     <x:row r="14" spans="1:10" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
@@ -2085,13 +2077,13 @@
     </x:row>
     <x:row r="15" spans="1:10" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D15" s="1" t="b">
         <x:v>1</x:v>
@@ -2108,13 +2100,13 @@
     </x:row>
     <x:row r="16" spans="1:10" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D16" s="1" t="b">
         <x:v>1</x:v>
@@ -2131,13 +2123,13 @@
     </x:row>
     <x:row r="17" spans="1:10" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D17" s="1" t="b">
         <x:v>1</x:v>
@@ -2154,13 +2146,13 @@
     </x:row>
     <x:row r="18" spans="1:10" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D18" s="1" t="b">
         <x:v>1</x:v>
@@ -2177,13 +2169,13 @@
     </x:row>
     <x:row r="19" spans="1:10" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D19" s="1" t="b">
         <x:v>1</x:v>
@@ -2200,13 +2192,13 @@
     </x:row>
     <x:row r="20" spans="1:10" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D20" s="1" t="b">
         <x:v>1</x:v>
@@ -2223,13 +2215,13 @@
     </x:row>
     <x:row r="21" spans="1:12" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D21" s="1" t="b">
         <x:v>1</x:v>
@@ -2241,13 +2233,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H21" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J21" s="1">
         <x:v>2</x:v>
@@ -2261,13 +2253,13 @@
     </x:row>
     <x:row r="22" spans="1:12" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D22" s="1" t="b">
         <x:v>1</x:v>
@@ -2279,13 +2271,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H22" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="J22" s="1">
         <x:v>2</x:v>
@@ -2299,13 +2291,13 @@
     </x:row>
     <x:row r="23" spans="1:12" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D23" s="1" t="b">
         <x:v>1</x:v>
@@ -2328,13 +2320,13 @@
     </x:row>
     <x:row r="24" spans="1:12" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D24" s="1" t="b">
         <x:v>1</x:v>
@@ -2357,13 +2349,13 @@
     </x:row>
     <x:row r="25" spans="1:12" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D25" s="1" t="b">
         <x:v>1</x:v>
@@ -2386,13 +2378,13 @@
     </x:row>
     <x:row r="26" spans="1:12" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D26" s="1" t="b">
         <x:v>1</x:v>
@@ -2415,13 +2407,13 @@
     </x:row>
     <x:row r="27" spans="1:12" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D27" s="1" t="b">
         <x:v>1</x:v>
@@ -2444,13 +2436,13 @@
     </x:row>
     <x:row r="28" spans="1:12" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D28" s="1" t="b">
         <x:v>1</x:v>
@@ -2473,13 +2465,13 @@
     </x:row>
     <x:row r="29" spans="1:12" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D29" s="1" t="b">
         <x:v>1</x:v>
@@ -2502,13 +2494,13 @@
     </x:row>
     <x:row r="30" spans="1:12" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D30" s="1" t="b">
         <x:v>1</x:v>
@@ -2531,13 +2523,13 @@
     </x:row>
     <x:row r="31" spans="1:10" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D31" s="1" t="b">
         <x:v>1</x:v>
@@ -2549,13 +2541,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H31" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J31" s="1">
         <x:v>0</x:v>
@@ -2563,13 +2555,13 @@
     </x:row>
     <x:row r="32" spans="1:10" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D32" s="1" t="b">
         <x:v>1</x:v>
@@ -2581,13 +2573,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H32" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J32" s="1">
         <x:v>0</x:v>
@@ -2595,13 +2587,13 @@
     </x:row>
     <x:row r="33" spans="1:10" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D33" s="1" t="b">
         <x:v>1</x:v>
@@ -2613,13 +2605,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H33" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="J33" s="1">
         <x:v>0</x:v>
@@ -2627,13 +2619,13 @@
     </x:row>
     <x:row r="34" spans="1:10" customHeight="1">
       <x:c r="A34" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D34" s="1" t="b">
         <x:v>1</x:v>
@@ -2645,13 +2637,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H34" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J34" s="1">
         <x:v>0</x:v>
@@ -2659,13 +2651,13 @@
     </x:row>
     <x:row r="35" spans="1:10" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D35" s="1" t="b">
         <x:v>1</x:v>
@@ -2677,13 +2669,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H35" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J35" s="1">
         <x:v>0</x:v>
@@ -2691,13 +2683,13 @@
     </x:row>
     <x:row r="36" spans="1:10" customHeight="1">
       <x:c r="A36" t="s">
-        <x:v>38</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>104</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D36" s="1" t="b">
         <x:v>0</x:v>
@@ -2714,13 +2706,13 @@
     </x:row>
     <x:row r="37" spans="1:10" customHeight="1">
       <x:c r="A37" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B37" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C37" s="1" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="D37" s="1" t="b">
         <x:v>0</x:v>
@@ -2737,13 +2729,13 @@
     </x:row>
     <x:row r="38" spans="1:10" customHeight="1">
       <x:c r="A38" t="s">
-        <x:v>33</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>77</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D38" s="1" t="b">
         <x:v>0</x:v>
@@ -2760,10 +2752,10 @@
     </x:row>
     <x:row r="39" spans="1:10" customHeight="1">
       <x:c r="A39" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B39" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="B39" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>142</x:v>
